--- a/artfynd/A 30671-2023 artfynd.xlsx
+++ b/artfynd/A 30671-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30671-2023 artfynd.xlsx
+++ b/artfynd/A 30671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111416525</v>
+        <v>90903814</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>359095.1406046218</v>
+        <v>359088</v>
       </c>
       <c r="R2" t="n">
-        <v>6393212.639220579</v>
+        <v>6393197</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>även bladrosetter på 1 kvm</t>
+          <t>Födosöksspår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,76 +770,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111416526</v>
+        <v>127800341</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+          <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>359094.3997885482</v>
+        <v>358965</v>
       </c>
       <c r="R3" t="n">
-        <v>6393206.775113393</v>
+        <v>6393308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,27 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>även ca 30 bladrosetter</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,27 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111416521</v>
+        <v>90903815</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,17 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -991,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>359101.3469427949</v>
+        <v>359096</v>
       </c>
       <c r="R4" t="n">
-        <v>6393205.997596246</v>
+        <v>6393189</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,27 +966,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>även ca 30 bladrosetter</t>
+          <t>Täcker cirka 2x3 meter. Tre med blommställningar. Drygt hundra säkerligen betydligt fler.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,27 +991,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111416528</v>
+        <v>111416521</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,12 +1033,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>359092.1819271583</v>
+        <v>359101</v>
       </c>
       <c r="R5" t="n">
-        <v>6393204.710604292</v>
+        <v>6393206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,19 +1085,14 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>även ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,12 +1122,7 @@
         <v>111416523</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>359100.0376043977</v>
+        <v>359100</v>
       </c>
       <c r="R6" t="n">
-        <v>6393214.610374114</v>
+        <v>6393215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,19 +1201,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1317,6 +1232,691 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111416525</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>359095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6393213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>även bladrosetter på 1 kvm</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111416526</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>359094</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6393206</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>även ca 30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111416528</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>359092</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6393204</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111416529</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>359096</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6393198</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>även bladrosetter på 3 kvm</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111416531</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörkaremossen, Enesberg/Eneslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>359099</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6393195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116087142</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Enesberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>359087</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6393192</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Det här är ett bestånd som ligger några meter längre söder än de som registrerades tidigare. Även de andra bestånd återbesöktes och räknades (inkl den här) till 713 plantor fördelade på  10 bestånd. Minst ett tidigare bestånd hittades inte den här gången.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30671-2023 artfynd.xlsx
+++ b/artfynd/A 30671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1918,6 +1918,103 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134599058</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bollebygd och Härryda kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>359092</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6393208</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30671-2023 artfynd.xlsx
+++ b/artfynd/A 30671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903814</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127800341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903815</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416521</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416525</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416526</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416528</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,6 +1731,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416529</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111416531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116087142</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,8 +2074,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>